--- a/erp-server/erp-server-file/src/main/resources/excel/dmp/adsErpInventoryDetailPlatformExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/dmp/adsErpInventoryDetailPlatformExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -77,7 +77,7 @@
     <t>{.erpWarehouseName}</t>
   </si>
   <si>
-    <t>{.realQty}</t>
+    <t>{.actualQty}</t>
   </si>
   <si>
     <t>{.usableQty}</t>
